--- a/Inventory_batch03.xlsx
+++ b/Inventory_batch03.xlsx
@@ -438,14 +438,14 @@
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="35" customWidth="1" min="18" max="18"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="35" customWidth="1" min="20" max="20"/>
+    <col width="40" customWidth="1" min="20" max="20"/>
     <col width="55" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
     <col width="16" customWidth="1" min="23" max="23"/>
@@ -469,7 +469,7 @@
     <col width="16" customWidth="1" min="41" max="41"/>
     <col width="16" customWidth="1" min="42" max="42"/>
     <col width="16" customWidth="1" min="43" max="43"/>
-    <col width="90" customWidth="1" min="44" max="44"/>
+    <col width="95" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -746,15 +746,35 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Wolf Creek Basin</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>E+M</t>
+        </is>
+      </c>
       <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>S+SS</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>(Perched) WT/GW dynamics and changes in GW storage; IEOF; Lateral flow; Matrix flow; Pipe flow; Preferential flow (no specifica vert/lat); Slow/deep SubFlow; SubFlow; Vertical flow</t>
+        </is>
+      </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
           <t>Y</t>
@@ -882,7 +902,7 @@
       </c>
       <c r="AR2" s="2" t="inlineStr">
         <is>
-          <t>Wolf Creek Research Basin has a public FRDR data release and official site documenting precipitation, streamflow, soil moisture profiles, groundwater well water levels, stream/rain isotopes, snow depth and SWE. EC was not verified.</t>
+          <t>Wolf Creek Research Basin has a public FRDR data release and official site documenting precipitation, streamflow, soil moisture profiles, groundwater well water levels, stream/rain isotopes, snow depth and SWE. EC was not verified. Penna supporting match: Wolf Creek Basin (Carey and Woo, 1999); Penna evidence was used only for Observed flags, not public access. Official/project source override applied for public-data status.</t>
         </is>
       </c>
     </row>
@@ -938,15 +958,39 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Krycklan C1; Krycklan C10; Krycklan C12; Krycklan C13; Krycklan C14; Krycklan C15; Krycklan C16; Krycklan C2 (+8 more)</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>131; 152</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Iso</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>S; S+SS</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>(Perched) WT/GW dynamics and changes in GW storage; Dynamics of saturated areas; IEOF; Lateral flow; Preferential flow (no specifica vert/lat); SubFlow</t>
+        </is>
+      </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
           <t>Partial</t>
@@ -1029,12 +1073,12 @@
       </c>
       <c r="AI3" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AJ3" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AK3" s="2" t="inlineStr">
@@ -1074,7 +1118,7 @@
       </c>
       <c r="AR3" s="2" t="inlineStr">
         <is>
-          <t>SLU/SITES provides Krycklan climate, runoff/water-balance and stream chemistry downloads including conductivity and 18O; infrastructure pages document precipitation as rain/snow, snowmelt sampling and groundwater wells. Groundwater data are stated as available on request; direct soil moisture data were not verified.</t>
+          <t>SLU/SITES provides Krycklan climate, runoff/water-balance and stream chemistry downloads including conductivity and 18O; infrastructure pages document precipitation as rain/snow, snowmelt sampling and groundwater wells. Groundwater data are stated as available on request; direct soil moisture data were not verified. Penna supporting match: Krycklan C1; Krycklan C10; Krycklan C12; Krycklan C13; Krycklan C14; Krycklan C15; Krycklan C16; Krycklan C2 (+8 more) (Laudon et al., 2007; Karlsten et al., 2016); Penna evidence was used only for Observed flags, not public access. Official/project source override applied for public-data status.</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1174,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
+          <t>No high-confidence match</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
@@ -1266,7 +1310,7 @@
       </c>
       <c r="AR4" s="2" t="inlineStr">
         <is>
-          <t>Girnock/Bruntland Burn sources document precipitation, discharge, soil moisture, groundwater wells and daily/weekly water isotopes; Aberdeen provides an isotope dataset and Scottish Government provides a weather/discharge dataset for a 2013 period. Long-term soil moisture and groundwater downloads were not verified.</t>
+          <t>Girnock/Bruntland Burn sources document precipitation, discharge, soil moisture, groundwater wells and daily/weekly water isotopes; Aberdeen provides an isotope dataset and Scottish Government provides a weather/discharge dataset for a 2013 period. Long-term soil moisture and groundwater downloads were not verified. No high-confidence Penna catchment match found in available Part2 fuzzy matching.</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1366,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
+          <t>No high-confidence match</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
@@ -1458,7 +1502,7 @@
       </c>
       <c r="AR5" s="2" t="inlineStr">
         <is>
-          <t>Fudoji publications document precipitation, spring/stream discharge, bedrock groundwater levels in boreholes, water sampling, stable isotopes and solute/chemistry data; AGU abstract reports 61 borehole wells and eight subcatchments. No public data repository was identified.</t>
+          <t>Fudoji publications document precipitation, spring/stream discharge, bedrock groundwater levels in boreholes, water sampling, stable isotopes and solute/chemistry data; AGU abstract reports 61 borehole wells and eight subcatchments. No public data repository was identified. No high-confidence Penna catchment match found in available Part2 fuzzy matching.</t>
         </is>
       </c>
     </row>
@@ -1514,14 +1558,30 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Brugga</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
       <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="R6" s="2" t="inlineStr"/>
       <c r="S6" s="2" t="inlineStr">
         <is>
@@ -1640,7 +1700,7 @@
       </c>
       <c r="AP6" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AQ6" s="2" t="inlineStr">
@@ -1650,7 +1710,7 @@
       </c>
       <c r="AR6" s="2" t="inlineStr">
         <is>
-          <t>Brugga sources document precipitation, discharge, snow-influenced runoff, wells/shallow groundwater, saturated source areas, EC/major ions and isotopes/tracers. Data appear project-held or regional gauge based; a complete open repository was not found.</t>
+          <t>Brugga sources document precipitation, discharge, snow-influenced runoff, wells/shallow groundwater, saturated source areas, EC/major ions and isotopes/tracers. Data appear project-held or regional gauge based; a complete open repository was not found. Penna supporting match: Brugga (Garvelmann et al., 2015); Penna evidence was used only for Observed flags, not public access.</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1766,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
+          <t>No high-confidence match</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr"/>
@@ -1842,7 +1902,7 @@
       </c>
       <c r="AR7" s="2" t="inlineStr">
         <is>
-          <t>Austria eHYD provides free public hydrographic station time series including precipitation and runoff. Specialized Dornbirnerach soil moisture, groundwater, isotope, EC, or snow/SWE observations were not verified from official sources.</t>
+          <t>Austria eHYD provides free public hydrographic station time series including precipitation and runoff. Specialized Dornbirnerach soil moisture, groundwater, isotope, EC, or snow/SWE observations were not verified from official sources. No high-confidence Penna catchment match found in available Part2 fuzzy matching.</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1958,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
+          <t>No high-confidence match</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr"/>
@@ -2034,7 +2094,7 @@
       </c>
       <c r="AR8" s="2" t="inlineStr">
         <is>
-          <t>Austria eHYD provides free public precipitation and runoff station time series. For Gail, no watershed-specific public soil moisture, groundwater, isotope, EC, or snow/SWE dataset was verified.</t>
+          <t>Austria eHYD provides free public precipitation and runoff station time series. For Gail, no watershed-specific public soil moisture, groundwater, isotope, EC, or snow/SWE dataset was verified. No high-confidence Penna catchment match found in available Part2 fuzzy matching.</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2150,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
+          <t>No high-confidence match</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr"/>
@@ -2226,7 +2286,7 @@
       </c>
       <c r="AR9" s="2" t="inlineStr">
         <is>
-          <t>Austria eHYD provides free public precipitation and runoff station time series. For Wimitzbach, no watershed-specific public soil moisture, groundwater, isotope, EC, or snow/SWE dataset was verified.</t>
+          <t>Austria eHYD provides free public precipitation and runoff station time series. For Wimitzbach, no watershed-specific public soil moisture, groundwater, isotope, EC, or snow/SWE dataset was verified. No high-confidence Penna catchment match found in available Part2 fuzzy matching.</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2342,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
+          <t>No high-confidence match</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr"/>
@@ -2418,7 +2478,7 @@
       </c>
       <c r="AR10" s="2" t="inlineStr">
         <is>
-          <t>Austria eHYD provides free public precipitation and runoff station time series. For Perschling, no watershed-specific public soil moisture, groundwater, isotope, EC, or snow/SWE dataset was verified.</t>
+          <t>Austria eHYD provides free public precipitation and runoff station time series. For Perschling, no watershed-specific public soil moisture, groundwater, isotope, EC, or snow/SWE dataset was verified. No high-confidence Penna catchment match found in available Part2 fuzzy matching.</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2534,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
+          <t>No high-confidence match</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr"/>
@@ -2610,7 +2670,7 @@
       </c>
       <c r="AR11" s="2" t="inlineStr">
         <is>
-          <t>LTER/DEIMS Uhlirska/Bedrichov pages describe long-term precipitation/runoff chemistry, soil moisture/suction, groundwater level, stable isotopes, soil water, snow cover and chemical parameters. Portal evidence is strong, but direct open download status for each variable was not verified.</t>
+          <t>LTER/DEIMS Uhlirska/Bedrichov pages describe long-term precipitation/runoff chemistry, soil moisture/suction, groundwater level, stable isotopes, soil water, snow cover and chemical parameters. Portal evidence is strong, but direct open download status for each variable was not verified. No high-confidence Penna catchment match found in available Part2 fuzzy matching. Official/project source override applied for public-data status.</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2726,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
+          <t>No high-confidence match</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
@@ -2802,7 +2862,7 @@
       </c>
       <c r="AR12" s="2" t="inlineStr">
         <is>
-          <t>Huanjiang/Mulian karst sources identify CAS/CNERN field station monitoring and NESDC water-quality datasets for surface and groundwater; publications document soil-water movement, runoff and karst hydrology. Direct variable-level public downloads for Mulian rainfall/runoff/soil water were not fully verified.</t>
+          <t>Huanjiang/Mulian karst sources identify CAS/CNERN field station monitoring and NESDC water-quality datasets for surface and groundwater; publications document soil-water movement, runoff and karst hydrology. Direct variable-level public downloads for Mulian rainfall/runoff/soil water were not fully verified. No high-confidence Penna catchment match found in available Part2 fuzzy matching.</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2918,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
+          <t>No high-confidence match</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr"/>
@@ -2994,7 +3054,7 @@
       </c>
       <c r="AR13" s="2" t="inlineStr">
         <is>
-          <t>Weatherley reports describe a research catchment with met stations, soil moisture/tension sensors, groundwater sensors/boreholes, runoff plots, two stream weirs and rainfall/runoff isotopes. WRO/repository access appears registration/request based; no direct public dataset was verified.</t>
+          <t>Weatherley reports describe a research catchment with met stations, soil moisture/tension sensors, groundwater sensors/boreholes, runoff plots, two stream weirs and rainfall/runoff isotopes. WRO/repository access appears registration/request based; no direct public dataset was verified. No high-confidence Penna catchment match found in available Part2 fuzzy matching. Official/project source override applied for public-data status.</t>
         </is>
       </c>
     </row>
@@ -3050,14 +3110,30 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Brugga</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
       <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="R14" s="2" t="inlineStr"/>
       <c r="S14" s="2" t="inlineStr">
         <is>
@@ -3176,7 +3252,7 @@
       </c>
       <c r="AP14" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AQ14" s="2" t="inlineStr">
@@ -3186,7 +3262,7 @@
       </c>
       <c r="AR14" s="2" t="inlineStr">
         <is>
-          <t>Brugga fast-groundwater-response study documents wells, near-stream saturated-area discharge, hydraulic data, deuterium, silica and major ions/cations during events. Public data downloads were not identified beyond regional gauge/project access.</t>
+          <t>Brugga fast-groundwater-response study documents wells, near-stream saturated-area discharge, hydraulic data, deuterium, silica and major ions/cations during events. Public data downloads were not identified beyond regional gauge/project access. Penna supporting match: Brugga (Garvelmann et al., 2015); Penna evidence was used only for Observed flags, not public access.</t>
         </is>
       </c>
     </row>
@@ -3242,15 +3318,35 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
-      <c r="O15" s="2" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Huewelerbach</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
       <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>IEOF; Water movement through bedrock or at the soil/bedrock interface (either SubFlow or GW rise)</t>
+        </is>
+      </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3258,12 +3354,12 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4TU.ResearchData / Luxembourg catchment data</t>
+          <t>GFZ/FID GEO / Luxembourg hydrometric datasets</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>https://4tu.edu.hpc.n-helix.com/datasets/fa78665a-64f8-437e-9376-6792b21df05a</t>
+          <t>https://doi.org/10.5880/FIDGEO.2019.010</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
@@ -3313,12 +3409,12 @@
       </c>
       <c r="AE15" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AF15" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AG15" s="2" t="inlineStr">
@@ -3378,7 +3474,7 @@
       </c>
       <c r="AR15" s="2" t="inlineStr">
         <is>
-          <t>Huewelerbach/Huewerbach has public 4TU pluviometer data and Luxembourg hydrological collections; Attert/Luxembourg studies support discharge and isotope observations. Direct soil moisture, groundwater or EC data for Huewelerbach were not verified.</t>
+          <t>Huewelerbach/Huewerbach has public 4TU pluviometer data and Luxembourg hydrological collections; Attert/Luxembourg studies support discharge and isotope observations. Direct soil moisture, groundwater or EC data for Huewelerbach were not verified. Penna supporting match: Huewelerbach (Butzen et al., 2014); Penna evidence was used only for Observed flags, not public access. Official/project source override applied for public-data status.</t>
         </is>
       </c>
     </row>
@@ -3434,15 +3530,39 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Weierbach</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>10; 11; 44; 89; 90; 91; 92; 138; 139; 168; 217; 221</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>E; E+M</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Ions+EC; Iso; Others+Diatoms</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>S; S+SS; SS</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>(Perched) WT/GW dynamics and changes in GW storage; Ch. Precip; Dynamics of saturated areas; Filling of subsurface depressions /fill and spill; Lateral flow; Macropore flow (no specifical vert/lat); Matrix flow; Preferential flow (no specifica vert/lat); SEOF; Soil moisture- streamflow threshold; SubFlow; Subsurface hillslope-stream connectivity; Vertical flow; Vertical preferential flow; Water movement through bedrock or at the soil/bedrock interface (either SubFlow or GW rise)</t>
+        </is>
+      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3515,22 +3635,22 @@
       </c>
       <c r="AG16" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AH16" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AI16" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AJ16" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AK16" s="2" t="inlineStr">
@@ -3570,7 +3690,7 @@
       </c>
       <c r="AR16" s="2" t="inlineStr">
         <is>
-          <t>Weierbach has a public Zenodo hydrological/isotopic database with rainfall/throughfall, soil volumetric water content, groundwater levels, discharge and delta18O/delta2H; a separate Zenodo/ESSD dataset provides high-frequency groundwater physico-chemical parameters including EC.</t>
+          <t>Weierbach has a public Zenodo hydrological/isotopic database with rainfall/throughfall, soil volumetric water content, groundwater levels, discharge and delta18O/delta2H; a separate Zenodo/ESSD dataset provides high-frequency groundwater physico-chemical parameters including EC. Penna supporting match: Weierbach (Antonelli et al., 2020 1 and 2; Coles et al., 2016; Glaser et al., 2016, 2018, 2019, 2020; Klaus et al., 2015b; Martinez-Carreras et al.,  2015; Scaini et al., 2018; Segura et al., 2023); Penna evidence was used only for Observed flags, not public access. Official/project source override applied for public-data status.</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3746,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
+          <t>No high-confidence match</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr"/>
@@ -3642,7 +3762,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>GFZ/FID GEO and CAMELS-LUX / Luxembourg hydrometric data</t>
+          <t>GFZ/FID GEO / Luxembourg hydrometric datasets</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -3762,7 +3882,7 @@
       </c>
       <c r="AR17" s="2" t="inlineStr">
         <is>
-          <t>Wollefsbach has public Attert hydrometric discharge data and Luxembourg isotope study support. Direct soil moisture, groundwater, EC, or snow/SWE observations were not verified.</t>
+          <t>Wollefsbach has public Attert hydrometric discharge data and Luxembourg isotope study support. Direct soil moisture, groundwater, EC, or snow/SWE observations were not verified. No high-confidence Penna catchment match found in available Part2 fuzzy matching. Official/project source override applied for public-data status.</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3938,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
+          <t>No high-confidence match</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
@@ -3954,7 +4074,7 @@
       </c>
       <c r="AR18" s="2" t="inlineStr">
         <is>
-          <t>Yakou-related publication evidence documents liquid/solid precipitation at Yakou meteorological station, soil water at several depths, frozen-soil seeps and shallow subsurface-flow/runoff-plot samples. Public integrated Yakou data were not identified; related Qinghai-Tibet public datasets are for other catchments.</t>
+          <t>Yakou-related publication evidence documents liquid/solid precipitation at Yakou meteorological station, soil water at several depths, frozen-soil seeps and shallow subsurface-flow/runoff-plot samples. Public integrated Yakou data were not identified; related Qinghai-Tibet public datasets are for other catchments. No high-confidence Penna catchment match found in available Part2 fuzzy matching.</t>
         </is>
       </c>
     </row>
@@ -4010,15 +4130,35 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>North river</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
-      <c r="R19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>(Perched) WT/GW dynamics and changes in GW storage</t>
+        </is>
+      </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
           <t>N</t>
@@ -4081,12 +4221,12 @@
       </c>
       <c r="AE19" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AF19" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AG19" s="2" t="inlineStr">
@@ -4146,7 +4286,7 @@
       </c>
       <c r="AR19" s="2" t="inlineStr">
         <is>
-          <t>The Longxi River Experimental Watershed is represented by the cited publication, but searches did not locate an official public integrated monitoring repository. Rainfall and runoff observations are inferred from the runoff-generation study; other variables remain Unknown.</t>
+          <t>The Longxi River Experimental Watershed is represented by the cited publication, but searches did not locate an official public integrated monitoring repository. Rainfall and runoff observations are inferred from the runoff-generation study; other variables remain Unknown. Penna supporting match: North river (Clark et al., 2017); Penna evidence was used only for Observed flags, not public access.</t>
         </is>
       </c>
     </row>
@@ -4202,15 +4342,35 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>North river</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="2" t="inlineStr"/>
-      <c r="R20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>(Perched) WT/GW dynamics and changes in GW storage</t>
+        </is>
+      </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
           <t>Partial</t>
@@ -4218,7 +4378,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>CUAHSI HydroShare Duke Forest Research Watershed / Duke Forest</t>
+          <t>CUAHSI HydroShare Duke Forest Research Watershed</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4338,7 +4498,7 @@
       </c>
       <c r="AR20" s="2" t="inlineStr">
         <is>
-          <t>Duke Forest Research Watershed has a discoverable HydroShare archive but content files are permission restricted; Duke Forest pages indicate weather station downloads and soil moisture data by request/related lab. Rain, streamflow, soil moisture and groundwater are treated as observed/partial access; isotope evidence was not verified.</t>
+          <t>Duke Forest Research Watershed has a discoverable HydroShare archive but content files are permission restricted; Duke Forest pages indicate weather station downloads and soil moisture data by request/related lab. Rain, streamflow, soil moisture and groundwater are treated as observed/partial access; isotope evidence was not verified. Penna supporting match: North river (Clark et al., 2017); Penna evidence was used only for Observed flags, not public access. Official/project source override applied for public-data status.</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4554,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Not evaluated - Penna files unavailable in repository</t>
+          <t>No high-confidence match</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
@@ -4410,7 +4570,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>University of Padua Rio Vauz publications / project contact</t>
+          <t>University of Padua Rio Vauz publications/project</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -4530,7 +4690,7 @@
       </c>
       <c r="AR21" s="2" t="inlineStr">
         <is>
-          <t>Rio Vauz long-term monitoring publications and featured catchment page document rainfall, streamflow, soil moisture, shallow groundwater/piezometers, connectivity/saturated areas, stable isotopes, EC, snow/snowmelt and event sampling. Article page states download data not available; access appears by project contact/collaboration.</t>
+          <t>Rio Vauz long-term monitoring publications and featured catchment page document rainfall, streamflow, soil moisture, shallow groundwater/piezometers, connectivity/saturated areas, stable isotopes, EC, snow/snowmelt and event sampling. Article page states download data not available; access appears by project contact/collaboration. No high-confidence Penna catchment match found in available Part2 fuzzy matching. Official/project source override applied for public-data status.</t>
         </is>
       </c>
     </row>
@@ -4545,7 +4705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -4554,7 +4714,7 @@
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="35" customWidth="1" min="6" max="6"/>
-    <col width="90" customWidth="1" min="7" max="7"/>
+    <col width="95" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4617,7 +4777,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -4639,32 +4799,32 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Official_Repository</t>
+          <t>Penna_Part2</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>FRDR Wolf Creek dataset</t>
+          <t>Penna_globalsynthesis_DB_Part2_update_2026_01.csv</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.20383/101.0113</t>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Public data release</t>
+          <t>Catchment fuzzy match and runoff-process labels</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>ESSD states Wolf Creek dataset includes precipitation, streamflow, soil moisture, groundwater well and snow/SWE data.</t>
+          <t>Matched to Wolf Creek Basin with process labels: (Perched) WT/GW dynamics and changes in GW storage; IEOF; Lateral flow; Matrix flow; Pipe flow; Preferential flow (no specifica vert/lat); Slow/deep SubFlow; SubFlow; Vertical flow</t>
         </is>
       </c>
     </row>
@@ -4676,54 +4836,54 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Project_Website</t>
+          <t>Penna_Part1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Wolf Creek Research Basin official site</t>
+          <t>Penna_globalsynthesis_DB_Part1.csv</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>https://www.wolfcreekresearchbasin.ca/</t>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Project data availability</t>
+          <t>Reference-level approach/tracer/flow type</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Official WCRB website describes public data and research resources.</t>
+          <t>Reference IDs 37; approach=E+M; tracer=; flow=S+SS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Krycklan, Sweden</t>
+          <t>Wolf Creek, Canada</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Official_Repository</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>ProcessDatabase3-filtered.xlsx</t>
+          <t>FRDR Wolf Creek dataset</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/hyp.10412</t>
+          <t>https://doi.org/10.20383/101.0113</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -4733,34 +4893,34 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+          <t>Public data release</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+          <t>ESSD states Wolf Creek dataset includes precipitation, streamflow, soil moisture, groundwater well and snow/SWE data.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Krycklan, Sweden</t>
+          <t>Wolf Creek, Canada</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Official_Repository</t>
+          <t>Project_Website</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>SLU Krycklan data page</t>
+          <t>Wolf Creek Research Basin official site</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>https://www.slu.se/en/about-slu/organisation/departments/forest-ecology-management/research/disciplines/forest-landscape-biogeochemistry/research/krycklan-catchment-study/data/</t>
+          <t>https://www.wolfcreekresearchbasin.ca/</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -4770,19 +4930,19 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Official data portal</t>
+          <t>Project data availability</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>SLU lists runoff, water chemistry, meteorology, precipitation and groundwater access.</t>
+          <t>Official WCRB website describes public data and research resources.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Krycklan, Sweden</t>
+          <t>Wolf Creek, Canada</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -4792,34 +4952,34 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>SITES Krycklan discharge</t>
+          <t>FRDR / Wolf Creek Research Basin</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>https://meta.fieldsites.se/collections/2M74g6oPabfeXXoOkaiGbFs2</t>
+          <t>https://doi.org/10.20383/101.0113</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Discharge data</t>
+          <t>Official/project repository public-data status and variable availability</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>SITES collection provides Krycklan stream water balance/discharge datasets.</t>
+          <t>Wolf Creek public FRDR data release includes precipitation, streamflow, soil moisture profiles, groundwater well level, isotopes and snow/SWE data.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Girnock, Scotland, United Kingdom</t>
+          <t>Krycklan, Sweden</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -4839,7 +4999,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4856,96 +5016,96 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Girnock, Scotland, United Kingdom</t>
+          <t>Krycklan, Sweden</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Official_Repository</t>
+          <t>Penna_Part2</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Aberdeen Bruntland Burn isotope dataset</t>
+          <t>Penna_globalsynthesis_DB_Part2_update_2026_01.csv</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>https://abdn.elsevierpure.com/en/datasets/water-isotopes-at-bruntland-burn-catchment/</t>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Stable isotope dataset</t>
+          <t>Catchment fuzzy match and runoff-process labels</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Dataset includes deuterium and oxygen-18 in precipitation, stream, soil moisture, plant xylem and groundwater.</t>
+          <t>Matched to Krycklan C1; Krycklan C10; Krycklan C12; Krycklan C13; Krycklan C14; Krycklan C15; Krycklan C16; Krycklan C2 (+8 more) with process labels: (Perched) WT/GW dynamics and changes in GW storage; Dynamics of saturated areas; IEOF; Lateral flow; Preferential flow (no specifica vert/lat); SubFlow</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Girnock, Scotland, United Kingdom</t>
+          <t>Krycklan, Sweden</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Official_Repository</t>
+          <t>Penna_Part1</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Scottish Government Girnock weather/discharge data</t>
+          <t>Penna_globalsynthesis_DB_Part1.csv</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>https://data.marine.gov.scot/dataset/weather-station-river-temperature-and-discharge-data-girnock-burn-june-july-2013</t>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Weather and discharge data</t>
+          <t>Reference-level approach/tracer/flow type</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Dataset includes automated weather station files and river discharge at Girnock.</t>
+          <t>Reference IDs 131; 152; approach=E; tracer=Iso; flow=S; S+SS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Fudoji Experimental Watershed, Tanakami Mountain, Japan</t>
+          <t>Krycklan, Sweden</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Official_Repository</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>ProcessDatabase3-filtered.xlsx</t>
+          <t>SLU Krycklan data page</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/hyp.1133</t>
+          <t>https://www.slu.se/en/about-slu/organisation/departments/forest-ecology-management/research/disciplines/forest-landscape-biogeochemistry/research/krycklan-catchment-study/data/</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -4955,34 +5115,34 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+          <t>Official data portal</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+          <t>SLU lists runoff, water chemistry, meteorology, precipitation and groundwater access.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Fudoji Experimental Watershed, Tanakami Mountain, Japan</t>
+          <t>Krycklan, Sweden</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>Official_Repository</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Fudoji J-STAGE PDF</t>
+          <t>SITES Krycklan discharge</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>https://www.jstage.jst.go.jp/article/ijece/7/1/7_5/_pdf</t>
+          <t>https://meta.fieldsites.se/collections/2M74g6oPabfeXXoOkaiGbFs2</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -4992,56 +5152,56 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Hydrometric and isotope evidence</t>
+          <t>Discharge data</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Paper describes precipitation, discharge, groundwater level, water sampling and isotopes.</t>
+          <t>SITES collection provides Krycklan stream water balance/discharge datasets.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Fudoji Experimental Watershed, Tanakami Mountain, Japan</t>
+          <t>Krycklan, Sweden</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>Official_Repository</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Fudoji AGU abstract</t>
+          <t>SLU Krycklan / SITES data portal</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>https://agu.confex.com/agu/fm14/webprogram/Paper21072.html</t>
+          <t>https://www.slu.se/en/about-slu/organisation/departments/forest-ecology-management/research/disciplines/forest-landscape-biogeochemistry/research/krycklan-catchment-study/data/</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Borehole network and chemistry evidence</t>
+          <t>Official/project repository public-data status and variable availability</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Abstract documents 61 boreholes, precipitation, discharge, major ions and stable isotopes.</t>
+          <t>SLU/SITES provides public Krycklan climate, runoff/water balance and chemistry data including EC/18O; groundwater is request-mediated.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
+          <t>Girnock, Scotland, United Kingdom</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -5056,12 +5216,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/hyp.330</t>
+          <t>https://doi.org/10.1002/hyp.10412</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5078,22 +5238,22 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
+          <t>Girnock, Scotland, United Kingdom</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Project_Website</t>
+          <t>Official_Repository</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>University Freiburg Brugga process page</t>
+          <t>Aberdeen Bruntland Burn isotope dataset</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>http://www.hydrology.uni-freiburg.de/forsch/qbildung/d/er_chem_brugga_.htm</t>
+          <t>https://abdn.elsevierpure.com/en/datasets/water-isotopes-at-bruntland-burn-catchment/</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -5103,34 +5263,34 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Runoff-process evidence</t>
+          <t>Stable isotope dataset</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Project page describes Brugga hillslope groundwater and runoff generation studies.</t>
+          <t>Dataset includes deuterium and oxygen-18 in precipitation, stream, soil moisture, plant xylem and groundwater.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
+          <t>Girnock, Scotland, United Kingdom</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>Official_Repository</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Brugga fast groundwater response DOI</t>
+          <t>Scottish Government Girnock weather/discharge data</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/hyp.5686</t>
+          <t>https://data.marine.gov.scot/dataset/weather-station-river-temperature-and-discharge-data-girnock-burn-june-july-2013</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -5140,19 +5300,19 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Event hydrometric/tracer evidence</t>
+          <t>Weather and discharge data</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Publication documents wells, saturated-area discharge, deuterium, silica and ions.</t>
+          <t>Dataset includes automated weather station files and river discharge at Girnock.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Dornbirnerach, Austria</t>
+          <t>Fudoji Experimental Watershed, Tanakami Mountain, Japan</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -5167,12 +5327,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.2478/johh-2018-0010</t>
+          <t>https://doi.org/10.1002/hyp.1133</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5189,22 +5349,22 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Dornbirnerach, Austria</t>
+          <t>Fudoji Experimental Watershed, Tanakami Mountain, Japan</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Official_Repository</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Austria Hydrographisches Jahrbuch/eHYD</t>
+          <t>Fudoji J-STAGE PDF</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>https://wasser.gv.at/hydjb/</t>
+          <t>https://www.jstage.jst.go.jp/article/ijece/7/1/7_5/_pdf</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -5214,34 +5374,34 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Public rain/runoff data</t>
+          <t>Hydrometric and isotope evidence</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Austrian hydrographic portal provides public CSV time series for precipitation and runoff stations.</t>
+          <t>Paper describes precipitation, discharge, groundwater level, water sampling and isotopes.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Gail, Austria</t>
+          <t>Fudoji Experimental Watershed, Tanakami Mountain, Japan</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>ProcessDatabase3-filtered.xlsx</t>
+          <t>Fudoji AGU abstract</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.2478/johh-2018-0010</t>
+          <t>https://agu.confex.com/agu/fm14/webprogram/Paper21072.html</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -5251,145 +5411,145 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+          <t>Borehole network and chemistry evidence</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+          <t>Abstract documents 61 boreholes, precipitation, discharge, major ions and stable isotopes.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Gail, Austria</t>
+          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Official_Repository</t>
+          <t>McMillan</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Austria Hydrographisches Jahrbuch/eHYD</t>
+          <t>ProcessDatabase3-filtered.xlsx</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>https://wasser.gv.at/hydjb/</t>
+          <t>https://doi.org/10.1002/hyp.330</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Public rain/runoff data</t>
+          <t>Watershed metadata and Level-1 runoff process aggregation</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Austrian hydrographic portal provides public CSV time series for precipitation and runoff stations.</t>
+          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Wimitzbach, Austria</t>
+          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Penna_Part2</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>ProcessDatabase3-filtered.xlsx</t>
+          <t>Penna_globalsynthesis_DB_Part2_update_2026_01.csv</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.2478/johh-2018-0010</t>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+          <t>Catchment fuzzy match and runoff-process labels</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+          <t xml:space="preserve">Matched to Brugga with process labels: </t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Wimitzbach, Austria</t>
+          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Official_Repository</t>
+          <t>Penna_Part1</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Austria Hydrographisches Jahrbuch/eHYD</t>
+          <t>Penna_globalsynthesis_DB_Part1.csv</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>https://wasser.gv.at/hydjb/</t>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Public rain/runoff data</t>
+          <t>Reference-level approach/tracer/flow type</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Austrian hydrographic portal provides public CSV time series for precipitation and runoff stations.</t>
+          <t>Reference IDs 82; approach=E; tracer=; flow=S</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Perschling, Austria</t>
+          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>ProcessDatabase3-filtered.xlsx</t>
+          <t>Brugga experimental basin summary</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.2478/johh-2018-0010</t>
+          <t>https://www.hydrology.uni-freiburg.de/publika/band10-sum.html</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -5399,34 +5559,34 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+          <t>Tracer, precipitation, discharge, groundwater and source-area evidence</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+          <t>University Freiburg summary documents 18O/3H/tracer hydrograph separation, wells, runoff components and saturated areas.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Perschling, Austria</t>
+          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Official_Repository</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Austria Hydrographisches Jahrbuch/eHYD</t>
+          <t>Brugga precipitation-discharge modeling paper</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>https://wasser.gv.at/hydjb/</t>
+          <t>https://hal.science/hal-00298620v1/document</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -5436,34 +5596,34 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Public rain/runoff data</t>
+          <t>Rain, discharge and snow-influenced hydrology</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Austrian hydrographic portal provides public CSV time series for precipitation and runoff stations.</t>
+          <t>Paper describes Brugga rainfall stations, discharge data and snow-influenced runoff regime.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>UhlÃ­Å™skÃ¡, Czech Republic</t>
+          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Project_Website</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>ProcessDatabase3-filtered.xlsx</t>
+          <t>University Freiburg Brugga process page</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/hyp.14516</t>
+          <t>http://www.hydrology.uni-freiburg.de/forsch/qbildung/d/er_chem_brugga_.htm</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -5473,34 +5633,34 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+          <t>Runoff-process evidence</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+          <t>Project page describes Brugga hillslope groundwater and runoff generation studies.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>UhlÃ­Å™skÃ¡, Czech Republic</t>
+          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Project_Website</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>LTER Uhlirska/Bedrichov catchment</t>
+          <t>Brugga fast groundwater response DOI</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>https://lter.cz/en/uhlirska-catchment</t>
+          <t>https://doi.org/10.1002/hyp.5686</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -5510,34 +5670,34 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Long-term observatory evidence</t>
+          <t>Event hydrometric/tracer evidence</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>LTER page describes monitored precipitation, runoff, soil, groundwater, isotopes and water chemistry.</t>
+          <t>Publication documents wells, saturated-area discharge, deuterium, silica and ions.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>UhlÃ­Å™skÃ¡, Czech Republic</t>
+          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Project_Website</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>DEIMS Bedrichov-Uhlirska</t>
+          <t>Brugga fast groundwater response DOI</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>https://deims.org/58923a61-9633-4d06-b147-65d45d2919d3</t>
+          <t>https://doi.org/10.1002/hyp.5686</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -5547,34 +5707,34 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Monitoring variables</t>
+          <t>Event hydrometric/tracer evidence</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>DEIMS page lists soil moisture, runoff, groundwater, stable isotopes and chemical parameters.</t>
+          <t>Publication documents rapid shallow groundwater response and tracer observations in Brugga.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Mulian watershed, Huanjiang county, Guangxi, China</t>
+          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Project_Website</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>ProcessDatabase3-filtered.xlsx</t>
+          <t>University Freiburg Brugga process page</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.jhydrol.2019.124370</t>
+          <t>http://www.hydrology.uni-freiburg.de/forsch/qbildung/d/er_chem_brugga_.htm</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -5584,56 +5744,56 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+          <t>Runoff-process evidence</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+          <t>Project page describes Brugga hillslope groundwater and source-area runoff studies.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Mulian watershed, Huanjiang county, Guangxi, China</t>
+          <t>Dornbirnerach, Austria</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Project_Website</t>
+          <t>McMillan</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>DEIMS Huanjiang Karst station</t>
+          <t>ProcessDatabase3-filtered.xlsx</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>https://deims.org/013f0ab4-a999-40ff-960d-2a8f89428969</t>
+          <t>https://doi.org/10.2478/johh-2018-0010</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Station monitoring context</t>
+          <t>Watershed metadata and Level-1 runoff process aggregation</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>DEIMS describes Huanjiang CAS/CNERN karst observation station.</t>
+          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Mulian watershed, Huanjiang county, Guangxi, China</t>
+          <t>Dornbirnerach, Austria</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -5643,12 +5803,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>NESDC Huanjiang water-quality dataset</t>
+          <t>Austria Hydrographisches Jahrbuch/eHYD</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>https://www.nesdc.org.cn/sdo/detail?id=67e3ca047e2817391bd355a4</t>
+          <t>https://wasser.gv.at/hydjb/</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -5658,19 +5818,19 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Surface/groundwater quality data</t>
+          <t>Public rain/runoff data</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>NESDC lists Huanjiang surface and groundwater quality dataset for 2007-2023.</t>
+          <t>Austrian hydrographic portal provides public CSV time series for precipitation and runoff stations.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Weatherley catchment, South Africa</t>
+          <t>Gail, Austria</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -5685,12 +5845,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1623/hysj.53.1.65</t>
+          <t>https://doi.org/10.2478/johh-2018-0010</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -5707,22 +5867,22 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Weatherley catchment, South Africa</t>
+          <t>Gail, Austria</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>Official_Repository</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>WRC Weatherley report</t>
+          <t>Austria Hydrographisches Jahrbuch/eHYD</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>https://www.wrc.org.za/wp-content/uploads/mdocs/1320%20web-Catchment%20hydrology1.pdf</t>
+          <t>https://wasser.gv.at/hydjb/</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -5732,71 +5892,71 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Weatherley instrumentation and isotope evidence</t>
+          <t>Public rain/runoff data</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Report documents met stations, soil moisture, groundwater sensors, runoff plots, stream weirs and rainfall/runoff isotopes.</t>
+          <t>Austrian hydrographic portal provides public CSV time series for precipitation and runoff stations.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Weatherley catchment, South Africa</t>
+          <t>Wimitzbach, Austria</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Project_Website</t>
+          <t>McMillan</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Water Research Observatory</t>
+          <t>ProcessDatabase3-filtered.xlsx</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>https://www.waterresearchobservatory.org/</t>
+          <t>https://doi.org/10.2478/johh-2018-0010</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Potential request/registration access</t>
+          <t>Watershed metadata and Level-1 runoff process aggregation</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>WRO hosts South African water datasets with registration/discovery workflow.</t>
+          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
+          <t>Wimitzbach, Austria</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Official_Repository</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>ProcessDatabase3-filtered.xlsx</t>
+          <t>Austria Hydrographisches Jahrbuch/eHYD</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/hyp.5686</t>
+          <t>https://wasser.gv.at/hydjb/</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -5806,71 +5966,71 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+          <t>Public rain/runoff data</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+          <t>Austrian hydrographic portal provides public CSV time series for precipitation and runoff stations.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
+          <t>Perschling, Austria</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>McMillan</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Brugga fast groundwater response DOI</t>
+          <t>ProcessDatabase3-filtered.xlsx</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/hyp.5686</t>
+          <t>https://doi.org/10.2478/johh-2018-0010</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Event hydrometric/tracer evidence</t>
+          <t>Watershed metadata and Level-1 runoff process aggregation</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Publication documents rapid shallow groundwater response and tracer observations in Brugga.</t>
+          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
+          <t>Perschling, Austria</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Project_Website</t>
+          <t>Official_Repository</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>University Freiburg Brugga process page</t>
+          <t>Austria Hydrographisches Jahrbuch/eHYD</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>http://www.hydrology.uni-freiburg.de/forsch/qbildung/d/er_chem_brugga_.htm</t>
+          <t>https://wasser.gv.at/hydjb/</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -5880,19 +6040,19 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Runoff-process evidence</t>
+          <t>Public rain/runoff data</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Project page describes Brugga hillslope groundwater and source-area runoff studies.</t>
+          <t>Austrian hydrographic portal provides public CSV time series for precipitation and runoff stations.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Huewelerbach catchments, Luxembourg</t>
+          <t>UhlÃ­Å™skÃ¡, Czech Republic</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -5907,12 +6067,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/hyp.10393</t>
+          <t>https://doi.org/10.1002/hyp.14516</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -5929,22 +6089,22 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Huewelerbach catchments, Luxembourg</t>
+          <t>UhlÃ­Å™skÃ¡, Czech Republic</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Official_Repository</t>
+          <t>Project_Website</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>4TU Huewerbach pluviometer dataset</t>
+          <t>LTER Uhlirska/Bedrichov catchment</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>https://4tu.edu.hpc.n-helix.com/datasets/fa78665a-64f8-437e-9376-6792b21df05a</t>
+          <t>https://lter.cz/en/uhlirska-catchment</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -5954,34 +6114,34 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Public precipitation data</t>
+          <t>Long-term observatory evidence</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>4TU dataset provides pluviometer data in Huewerbach/Huewelerbach basin.</t>
+          <t>LTER page describes monitored precipitation, runoff, soil, groundwater, isotopes and water chemistry.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Huewelerbach catchments, Luxembourg</t>
+          <t>UhlÃ­Å™skÃ¡, Czech Republic</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Official_Repository</t>
+          <t>Project_Website</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Darelux Luxembourg hydrology collection</t>
+          <t>DEIMS Bedrichov-Uhlirska</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>https://4tu.edu.hpc.n-helix.com/collections/aedfc560-9b08-433b-ad55-7658a7e1df6a</t>
+          <t>https://deims.org/58923a61-9633-4d06-b147-65d45d2919d3</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -5991,108 +6151,108 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Hydrological collection context</t>
+          <t>Monitoring variables</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>4TU collection lists Luxembourg hydrological measurement datasets.</t>
+          <t>DEIMS page lists soil moisture, runoff, groundwater, stable isotopes and chemical parameters.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Weierbach catchment, Luxembourg</t>
+          <t>UhlÃ­Å™skÃ¡, Czech Republic</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Official_Repository</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>ProcessDatabase3-filtered.xlsx</t>
+          <t>LTER/DEIMS Bedrichov-Uhlirska catchment</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/hyp.10393</t>
+          <t>https://lter.cz/en/uhlirska-catchment</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+          <t>Official/project repository public-data status and variable availability</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+          <t>LTER/DEIMS Uhlirska documents precipitation/runoff, soil moisture/suction, groundwater, isotopes, chemistry and snow cover; variable-level download access is partly unclear.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Weierbach catchment, Luxembourg</t>
+          <t>Mulian watershed, Huanjiang county, Guangxi, China</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Official_Repository</t>
+          <t>McMillan</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Weierbach Zenodo hydrological/isotope database</t>
+          <t>ProcessDatabase3-filtered.xlsx</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.4537700</t>
+          <t>https://doi.org/10.1016/j.jhydrol.2019.124370</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Public hydrology and isotope database</t>
+          <t>Watershed metadata and Level-1 runoff process aggregation</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Weierbach paper states hydrological and isotopic database is public on Zenodo.</t>
+          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Weierbach catchment, Luxembourg</t>
+          <t>Mulian watershed, Huanjiang county, Guangxi, China</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Official_Repository</t>
+          <t>Project_Website</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Weierbach groundwater physico-chemical Zenodo</t>
+          <t>DEIMS Huanjiang Karst station</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.10869166</t>
+          <t>https://deims.org/013f0ab4-a999-40ff-960d-2a8f89428969</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -6102,34 +6262,34 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Public groundwater EC and chemistry</t>
+          <t>Station monitoring context</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>ESSD paper states high-frequency groundwater physico-chemical data are public on Zenodo.</t>
+          <t>DEIMS describes Huanjiang CAS/CNERN karst observation station.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Wollefsbach, Luxembourg</t>
+          <t>Mulian watershed, Huanjiang county, Guangxi, China</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Official_Repository</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>ProcessDatabase3-filtered.xlsx</t>
+          <t>NESDC Huanjiang water-quality dataset</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/hyp.10393</t>
+          <t>https://www.nesdc.org.cn/sdo/detail?id=67e3ca047e2817391bd355a4</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -6139,56 +6299,56 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+          <t>Surface/groundwater quality data</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+          <t>NESDC lists Huanjiang surface and groundwater quality dataset for 2007-2023.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Wollefsbach, Luxembourg</t>
+          <t>Weatherley catchment, South Africa</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Official_Repository</t>
+          <t>McMillan</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>GFZ/FID GEO streamflow intermittency dataset</t>
+          <t>ProcessDatabase3-filtered.xlsx</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5880/FIDGEO.2019.010</t>
+          <t>https://doi.org/10.1623/hysj.53.1.65</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Public Wollefsbach discharge</t>
+          <t>Watershed metadata and Level-1 runoff process aggregation</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Dataset includes discharge for Wollefsbach among Attert subcatchments.</t>
+          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Wollefsbach, Luxembourg</t>
+          <t>Weatherley catchment, South Africa</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -6198,12 +6358,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Luxembourg isotope study</t>
+          <t>WRC Weatherley report</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://hess.copernicus.org/articles/30/343/2026/</t>
+          <t>https://www.wrc.org.za/wp-content/uploads/mdocs/1320%20web-Catchment%20hydrology1.pdf</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -6213,34 +6373,34 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Isotope support</t>
+          <t>Weatherley instrumentation and isotope evidence</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Publication reports precipitation and streamflow isotopes for nested Luxembourg catchments.</t>
+          <t>Report documents met stations, soil moisture, groundwater sensors, runoff plots, stream weirs and rainfall/runoff isotopes.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Yakou catchment, Qinghai, China</t>
+          <t>Weatherley catchment, South Africa</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Project_Website</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>ProcessDatabase3-filtered.xlsx</t>
+          <t>Water Research Observatory</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/hyp.13650</t>
+          <t>https://www.waterresearchobservatory.org/</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -6250,56 +6410,56 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+          <t>Potential request/registration access</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+          <t>WRO hosts South African water datasets with registration/discovery workflow.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Yakou catchment, Qinghai, China</t>
+          <t>Weatherley catchment, South Africa</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>Official_Repository</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Yakou/Binggou permafrost catchment paper</t>
+          <t>Weatherley Database / WRC Water Research Observatory</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>https://www.mdpi.com/2073-4441/14/18/2782</t>
+          <t>https://www.waterresearchobservatory.org/</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Rain, snow, soil water and runoff evidence</t>
+          <t>Official/project repository public-data status and variable availability</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Paper documents Yakou precipitation, soil water and shallow subsurface-flow samples.</t>
+          <t>Weatherley reports document met stations, soil moisture/tension sensors, groundwater sensors/boreholes, runoff plots, stream weirs and isotopes; access appears registration/request based.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Longxi River Experimental Watershed, northwest of Chengdu city, Sichuan, China</t>
+          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -6314,12 +6474,12 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.jhydrol.2021.127107</t>
+          <t>https://doi.org/10.1002/hyp.5686</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6336,96 +6496,96 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Longxi River Experimental Watershed, northwest of Chengdu city, Sichuan, China</t>
+          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>Penna_Part2</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Longxi River Experimental Watershed DOI</t>
+          <t>Penna_globalsynthesis_DB_Part2_update_2026_01.csv</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.jhydrol.2021.127107</t>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Rainfall-runoff study evidence</t>
+          <t>Catchment fuzzy match and runoff-process labels</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Cited publication is used as evidence for Longxi experimental watershed rainfall-runoff observations.</t>
+          <t xml:space="preserve">Matched to Brugga with process labels: </t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Duke Forest Research Watershed, North Carolina, United States</t>
+          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Penna_Part1</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>ProcessDatabase3-filtered.xlsx</t>
+          <t>Penna_globalsynthesis_DB_Part1.csv</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/2016WR019742</t>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+          <t>Reference-level approach/tracer/flow type</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+          <t>Reference IDs 82; approach=E; tracer=; flow=S</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Duke Forest Research Watershed, North Carolina, United States</t>
+          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Official_Repository</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Duke Forest Research Watershed HydroShare</t>
+          <t>Brugga experimental basin summary</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>https://www.hydroshare.org/resource/673017a70dd94807ad40b1331a1f9afc/</t>
+          <t>https://www.hydrology.uni-freiburg.de/publika/band10-sum.html</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -6435,34 +6595,34 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Discoverable restricted archive</t>
+          <t>Tracer, precipitation, discharge, groundwater and source-area evidence</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>HydroShare archive is discoverable but content requires permission/contact.</t>
+          <t>University Freiburg summary documents 18O/3H/tracer hydrograph separation, wells, runoff components and saturated areas.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Duke Forest Research Watershed, North Carolina, United States</t>
+          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Project_Website</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Duke Forest available data</t>
+          <t>Brugga precipitation-discharge modeling paper</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>http://dukeforest.duke.edu/research/available-data/</t>
+          <t>https://hal.science/hal-00298620v1/document</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -6472,34 +6632,34 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Request-based data evidence</t>
+          <t>Rain, discharge and snow-influenced hydrology</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Duke Forest page describes weather-station downloads and soil moisture data availability/request procedures.</t>
+          <t>Paper describes Brugga rainfall stations, discharge data and snow-influenced runoff regime.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Rio Vauz Basin, Italy</t>
+          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>Project_Website</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>ProcessDatabase3-filtered.xlsx</t>
+          <t>University Freiburg Brugga process page</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.18172/cig.3327</t>
+          <t>http://www.hydrology.uni-freiburg.de/forsch/qbildung/d/er_chem_brugga_.htm</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -6509,19 +6669,19 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+          <t>Runoff-process evidence</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+          <t>Project page describes Brugga hillslope groundwater and runoff generation studies.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Rio Vauz Basin, Italy</t>
+          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -6531,12 +6691,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Rio Vauz long-term monitoring article</t>
+          <t>Brugga fast groundwater response DOI</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>https://publicaciones.unirioja.es/ojs/index.php/cig/article/view/3327</t>
+          <t>https://doi.org/10.1002/hyp.5686</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -6546,49 +6706,1344 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Long-term monitoring and tracer evidence</t>
+          <t>Event hydrometric/tracer evidence</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Article documents hydrological monitoring, soil moisture, water table, EC and stable isotopes; page states data download unavailable.</t>
+          <t>Publication documents wells, saturated-area discharge, deuterium, silica and ions.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Brugga fast groundwater response DOI</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/hyp.5686</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Event hydrometric/tracer evidence</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Publication documents rapid shallow groundwater response and tracer observations in Brugga.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Brugga experimental basin, Black Forest Mountains, Germany</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Project_Website</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>University Freiburg Brugga process page</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>http://www.hydrology.uni-freiburg.de/forsch/qbildung/d/er_chem_brugga_.htm</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Runoff-process evidence</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Project page describes Brugga hillslope groundwater and source-area runoff studies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Huewelerbach catchments, Luxembourg</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>McMillan</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>ProcessDatabase3-filtered.xlsx</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/hyp.10393</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Huewelerbach catchments, Luxembourg</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Penna_Part2</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Penna_globalsynthesis_DB_Part2_update_2026_01.csv</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Catchment fuzzy match and runoff-process labels</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Matched to Huewelerbach with process labels: IEOF; Water movement through bedrock or at the soil/bedrock interface (either SubFlow or GW rise)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Huewelerbach catchments, Luxembourg</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Penna_Part1</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Penna_globalsynthesis_DB_Part1.csv</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Reference-level approach/tracer/flow type</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Reference IDs 34; approach=E; tracer=; flow=S</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Huewelerbach catchments, Luxembourg</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Official_Repository</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>4TU Huewerbach pluviometer dataset</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>https://4tu.edu.hpc.n-helix.com/datasets/fa78665a-64f8-437e-9376-6792b21df05a</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Public precipitation data</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>4TU dataset provides pluviometer data in Huewerbach/Huewelerbach basin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Huewelerbach catchments, Luxembourg</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Official_Repository</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Darelux Luxembourg hydrology collection</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>https://4tu.edu.hpc.n-helix.com/collections/aedfc560-9b08-433b-ad55-7658a7e1df6a</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Hydrological collection context</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>4TU collection lists Luxembourg hydrological measurement datasets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Huewelerbach catchments, Luxembourg</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Official_Repository</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>GFZ/FID GEO / Luxembourg hydrometric datasets</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5880/FIDGEO.2019.010</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Official/project repository public-data status and variable availability</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg/Attert datasets provide public discharge/hydrometeorological data; isotope studies support precipitation and stream-water isotope observations for nested catchments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Weierbach catchment, Luxembourg</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>McMillan</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>ProcessDatabase3-filtered.xlsx</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/hyp.10393</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Weierbach catchment, Luxembourg</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Penna_Part2</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Penna_globalsynthesis_DB_Part2_update_2026_01.csv</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Catchment fuzzy match and runoff-process labels</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Matched to Weierbach with process labels: (Perched) WT/GW dynamics and changes in GW storage; Ch. Precip; Dynamics of saturated areas; Filling of subsurface depressions /fill and spill; Lateral flow; Macropore flow (no specifical vert/lat); Matrix flow; Preferential flow (no specifica vert/lat); SEOF; Soil moisture- streamflow threshold; Su</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Weierbach catchment, Luxembourg</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Penna_Part1</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Penna_globalsynthesis_DB_Part1.csv</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Reference-level approach/tracer/flow type</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Reference IDs 10; 11; 44; 89; 90; 91; 92; 138; 139; 168; 217; 221; approach=E; E+M; tracer=Ions+EC; Iso; Others+Diatoms; flow=S; S+SS; SS</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Weierbach catchment, Luxembourg</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Official_Repository</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Weierbach Zenodo hydrological/isotope database</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.4537700</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Public hydrology and isotope database</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Weierbach paper states hydrological and isotopic database is public on Zenodo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Weierbach catchment, Luxembourg</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Official_Repository</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Weierbach groundwater physico-chemical Zenodo</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.10869166</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Public groundwater EC and chemistry</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>ESSD paper states high-frequency groundwater physico-chemical data are public on Zenodo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Weierbach catchment, Luxembourg</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Official_Repository</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Zenodo Weierbach Experimental Catchment</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.4537700</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Official/project repository public-data status and variable availability</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Weierbach public Zenodo database contains rainfall/throughfall, soil water content, groundwater levels, discharge and stable isotopes; separate Zenodo dataset includes groundwater EC/physico-chemistry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Wollefsbach, Luxembourg</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>McMillan</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>ProcessDatabase3-filtered.xlsx</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/hyp.10393</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Wollefsbach, Luxembourg</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Official_Repository</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>GFZ/FID GEO streamflow intermittency dataset</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5880/FIDGEO.2019.010</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Public discharge data for Wollefsbach/Attert subcatchments</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>ESSD dataset reports 15-minute discharge data for Wollefsbach among Attert subcatchments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Wollefsbach, Luxembourg</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg isotope study</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>https://hess.copernicus.org/articles/30/343/2026/</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Isotope observation evidence</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Publication reports fortnightly precipitation and streamflow stable isotopes in nested Luxembourg catchments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Wollefsbach, Luxembourg</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Official_Repository</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>GFZ/FID GEO streamflow intermittency dataset</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5880/FIDGEO.2019.010</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Public Wollefsbach discharge</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Dataset includes discharge for Wollefsbach among Attert subcatchments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Wollefsbach, Luxembourg</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg isotope study</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>https://hess.copernicus.org/articles/30/343/2026/</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Isotope support</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Publication reports precipitation and streamflow isotopes for nested Luxembourg catchments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Wollefsbach, Luxembourg</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Official_Repository</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>GFZ/FID GEO / Luxembourg hydrometric datasets</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5880/FIDGEO.2019.010</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Official/project repository public-data status and variable availability</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg/Attert datasets provide public discharge/hydrometeorological data; isotope studies support precipitation and stream-water isotope observations for nested catchments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Yakou catchment, Qinghai, China</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>McMillan</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>ProcessDatabase3-filtered.xlsx</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/hyp.13650</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Yakou catchment, Qinghai, China</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Yakou/Binggou permafrost catchment paper</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mdpi.com/2073-4441/14/18/2782</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Rain, snow, soil water and runoff evidence</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Paper documents Yakou precipitation, soil water and shallow subsurface-flow samples.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Longxi River Experimental Watershed, northwest of Chengdu city, Sichuan, China</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>McMillan</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>ProcessDatabase3-filtered.xlsx</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.jhydrol.2021.127107</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Longxi River Experimental Watershed, northwest of Chengdu city, Sichuan, China</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Penna_Part2</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Penna_globalsynthesis_DB_Part2_update_2026_01.csv</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Catchment fuzzy match and runoff-process labels</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Matched to North river with process labels: (Perched) WT/GW dynamics and changes in GW storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Longxi River Experimental Watershed, northwest of Chengdu city, Sichuan, China</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Penna_Part1</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Penna_globalsynthesis_DB_Part1.csv</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Reference-level approach/tracer/flow type</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Reference IDs 42; approach=M; tracer=; flow=S</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Longxi River Experimental Watershed, northwest of Chengdu city, Sichuan, China</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Longxi River Experimental Watershed DOI</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.jhydrol.2021.127107</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Rainfall-runoff study evidence</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Cited publication is used as evidence for Longxi experimental watershed rainfall-runoff observations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Duke Forest Research Watershed, North Carolina, United States</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>McMillan</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>ProcessDatabase3-filtered.xlsx</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/2016WR019742</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Duke Forest Research Watershed, North Carolina, United States</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Penna_Part2</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Penna_globalsynthesis_DB_Part2_update_2026_01.csv</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Catchment fuzzy match and runoff-process labels</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Matched to North river with process labels: (Perched) WT/GW dynamics and changes in GW storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Duke Forest Research Watershed, North Carolina, United States</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Penna_Part1</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Penna_globalsynthesis_DB_Part1.csv</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.15123553</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Reference-level approach/tracer/flow type</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Reference IDs 42; approach=M; tracer=; flow=S</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Duke Forest Research Watershed, North Carolina, United States</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Official_Repository</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Duke Forest Research Watershed HydroShare</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hydroshare.org/resource/673017a70dd94807ad40b1331a1f9afc/</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Discoverable restricted archive</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>HydroShare archive is discoverable but content requires permission/contact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Duke Forest Research Watershed, North Carolina, United States</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Project_Website</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Duke Forest available data</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>http://dukeforest.duke.edu/research/available-data/</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Request-based data evidence</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Duke Forest page describes weather-station downloads and soil moisture data availability/request procedures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Duke Forest Research Watershed, North Carolina, United States</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Official_Repository</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>CUAHSI HydroShare Duke Forest Research Watershed</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hydroshare.org/resource/673017a70dd94807ad40b1331a1f9afc/</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Official/project repository public-data status and variable availability</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Duke Forest HydroShare archive is discoverable but access-restricted; Duke Forest pages indicate weather and soil moisture data availability by request.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
           <t>Rio Vauz Basin, Italy</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>McMillan</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>ProcessDatabase3-filtered.xlsx</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.18172/cig.3327</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Watershed metadata and Level-1 runoff process aggregation</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Primary McMillan-derived row used for watershed metadata, citation and Level-1 runoff process flags.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Rio Vauz Basin, Italy</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Rio Vauz long-term monitoring article</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>https://publicaciones.unirioja.es/ojs/index.php/cig/article/view/3327</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Long-term monitoring and tracer evidence</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Article documents hydrological monitoring, soil moisture, water table, EC and stable isotopes; page states data download unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Rio Vauz Basin, Italy</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>Project_Website</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
         <is>
           <t>EGU Featured Catchment Rio Vauz</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>https://blogs.egu.eu/divisions/hs/2019/11/20/featured-catchment-series-the-rio-vauz-catchment-long-term-hydrologic-observations-in-the-dolomites/</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Project instrumentation details</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>Featured catchment page describes soil moisture, piezometers, isotopes, EC, snow and event sampling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Rio Vauz Basin, Italy</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Official_Repository</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>University of Padua Rio Vauz publications/project</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>https://publicaciones.unirioja.es/ojs/index.php/cig/article/view/3327</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Official/project repository public-data status and variable availability</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Rio Vauz publications document long-term rainfall, streamflow, soil moisture, piezometers, stable isotopes, EC and snow/snowmelt event sampling; data access appears by project contact/collaboration.</t>
         </is>
       </c>
     </row>
